--- a/documents/restaurant-form-testcases.xlsx
+++ b/documents/restaurant-form-testcases.xlsx
@@ -1,6 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18000" windowHeight="10000" activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet name="Auth_Users" sheetId="1" r:id="rId1"/>
     <sheet name="Menu_Categories" sheetId="2" r:id="rId2"/>
@@ -8,6 +12,7 @@
     <sheet name="Orders_Payments" sheetId="4" r:id="rId4"/>
     <sheet name="Reports_Dashboard" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1593,6 +1598,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7"/>
@@ -6159,6 +6168,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7"/>
@@ -10725,6 +10738,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7"/>
@@ -15291,6 +15308,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7"/>
@@ -19857,6 +19878,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7"/>
